--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122221675</v>
+        <v>122223396</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>43718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315754</v>
+        <v>315859</v>
       </c>
       <c r="R2" t="n">
-        <v>6552782</v>
+        <v>6552795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,22 +774,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blåbärbarrblandskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på högstubbe # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122223396</v>
+        <v>122221675</v>
       </c>
       <c r="B3" t="n">
-        <v>43718</v>
+        <v>90705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,36 +819,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315859</v>
+        <v>315754</v>
       </c>
       <c r="R3" t="n">
-        <v>6552795</v>
+        <v>6552782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Blåbärbarrblandskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fnöskticka på högstubbe # Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>122221675</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122223396</v>
+        <v>122221675</v>
       </c>
       <c r="B2" t="n">
-        <v>43718</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315859</v>
+        <v>315754</v>
       </c>
       <c r="R2" t="n">
-        <v>6552795</v>
+        <v>6552782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,22 +772,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Blåbärbarrblandskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fnöskticka på högstubbe # Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122221675</v>
+        <v>122223396</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>43718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,34 +817,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315754</v>
+        <v>315859</v>
       </c>
       <c r="R3" t="n">
-        <v>6552782</v>
+        <v>6552795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blåbärbarrblandskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på högstubbe # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122221675</v>
+        <v>122223396</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>43723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315754</v>
+        <v>315859</v>
       </c>
       <c r="R2" t="n">
-        <v>6552782</v>
+        <v>6552795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,22 +774,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blåbärbarrblandskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på högstubbe # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122223396</v>
+        <v>122221675</v>
       </c>
       <c r="B3" t="n">
-        <v>43718</v>
+        <v>90727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,36 +819,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315859</v>
+        <v>315754</v>
       </c>
       <c r="R3" t="n">
-        <v>6552795</v>
+        <v>6552782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Blåbärbarrblandskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fnöskticka på högstubbe # Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122223396</v>
+        <v>122221675</v>
       </c>
       <c r="B2" t="n">
-        <v>43723</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315859</v>
+        <v>315754</v>
       </c>
       <c r="R2" t="n">
-        <v>6552795</v>
+        <v>6552782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,22 +772,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Blåbärbarrblandskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fnöskticka på högstubbe # Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122221675</v>
+        <v>122223396</v>
       </c>
       <c r="B3" t="n">
-        <v>90727</v>
+        <v>43723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,34 +817,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315754</v>
+        <v>315859</v>
       </c>
       <c r="R3" t="n">
-        <v>6552782</v>
+        <v>6552795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blåbärbarrblandskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på högstubbe # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122221675</v>
+        <v>122223396</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>43723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
+        <v>101735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315754</v>
+        <v>315859</v>
       </c>
       <c r="R2" t="n">
-        <v>6552782</v>
+        <v>6552795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,22 +769,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blåbärbarrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på högstubbe # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122223396</v>
+        <v>122221675</v>
       </c>
       <c r="B3" t="n">
-        <v>43723</v>
+        <v>90736</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,36 +809,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Jättesvampmal</t>
-        </is>
+        <v>3242</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315859</v>
+        <v>315754</v>
       </c>
       <c r="R3" t="n">
-        <v>6552795</v>
+        <v>6552782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +889,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
+          <t>Blåbärbarrblandskog</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fnöskticka på högstubbe # Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122223396</v>
+        <v>122221675</v>
       </c>
       <c r="B2" t="n">
-        <v>43723</v>
+        <v>90749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>3242</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315859</v>
+        <v>315754</v>
       </c>
       <c r="R2" t="n">
-        <v>6552795</v>
+        <v>6552782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,17 +772,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Blåbärbarrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fnöskticka på högstubbe # Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122221675</v>
+        <v>122223396</v>
       </c>
       <c r="B3" t="n">
-        <v>90736</v>
+        <v>43727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,29 +817,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>101735</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315754</v>
+        <v>315859</v>
       </c>
       <c r="R3" t="n">
-        <v>6552782</v>
+        <v>6552795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,17 +904,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blåbärbarrblandskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på högstubbe # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122221675</v>
       </c>
       <c r="B2" t="n">
-        <v>90749</v>
+        <v>90762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122221675</v>
+        <v>122223396</v>
       </c>
       <c r="B2" t="n">
-        <v>90762</v>
+        <v>43727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315754</v>
+        <v>315859</v>
       </c>
       <c r="R2" t="n">
-        <v>6552782</v>
+        <v>6552795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,22 +774,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blåbärbarrblandskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på högstubbe # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122223396</v>
+        <v>122221675</v>
       </c>
       <c r="B3" t="n">
-        <v>43727</v>
+        <v>90762</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,36 +819,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315859</v>
+        <v>315754</v>
       </c>
       <c r="R3" t="n">
-        <v>6552795</v>
+        <v>6552782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Blåbärbarrblandskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fnöskticka på högstubbe # Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 59166-2024 artfynd.xlsx
+++ b/artfynd/A 59166-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>122221675</v>
       </c>
       <c r="B3" t="n">
-        <v>90762</v>
+        <v>90755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
